--- a/data/human/adult/validation/Scenarios/Showcases/CombatMultitraumaValidation.xlsx
+++ b/data/human/adult/validation/Scenarios/Showcases/CombatMultitraumaValidation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="26626"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27628"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Work\Source\Pulse\documentation\source\data\human\adult\validation\Scenarios\Showcases\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Work\Source\Pulse\release_updates\source\data\human\adult\validation\Scenarios\Showcases\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDA83272-30D4-4259-B784-9329E10AEF43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9017E730-2CFA-45D1-BDB1-8F4953ABF023}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="615" yWindow="7425" windowWidth="27840" windowHeight="22365" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-2955" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Combat Multitrauma" sheetId="7" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="55">
   <si>
     <t>A needle decompression procedure is applied on the affected side.</t>
   </si>
@@ -281,6 +281,9 @@
   </si>
   <si>
     <t>|&lt;span class="danger"&gt;</t>
+  </si>
+  <si>
+    <t>&lt;/span&gt;|&lt;span class="danger"&gt;</t>
   </si>
 </sst>
 </file>
@@ -1222,7 +1225,7 @@
         <v>26</v>
       </c>
       <c r="O7" s="7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="P7" s="10" t="s">
         <v>20</v>
